--- a/DHMT2026 - Phan chia chi tieu tai VCK 20260617.XLSX
+++ b/DHMT2026 - Phan chia chi tieu tai VCK 20260617.XLSX
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\App xep lich thi dau\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ntlon\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E43543A-A398-4178-AAD3-727B139B98C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA706E49-3F9C-4FD2-96AE-9242ACF05B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2329,77 +2329,81 @@
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2408,10 +2412,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2843,100 +2843,100 @@
       <c r="AS4" s="2"/>
     </row>
     <row r="5" spans="1:45" ht="56.25" customHeight="1">
-      <c r="A5" s="181" t="s">
+      <c r="A5" s="186" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="181" t="s">
+      <c r="C5" s="186" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="7"/>
-      <c r="E5" s="183" t="s">
+      <c r="E5" s="179" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="180"/>
-      <c r="G5" s="183" t="s">
+      <c r="G5" s="179" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="180"/>
-      <c r="I5" s="183" t="s">
+      <c r="I5" s="179" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="180"/>
-      <c r="K5" s="183" t="s">
+      <c r="K5" s="179" t="s">
         <v>7</v>
       </c>
       <c r="L5" s="180"/>
-      <c r="M5" s="183" t="s">
+      <c r="M5" s="179" t="s">
         <v>8</v>
       </c>
       <c r="N5" s="180"/>
-      <c r="O5" s="183" t="s">
+      <c r="O5" s="179" t="s">
         <v>9</v>
       </c>
       <c r="P5" s="180"/>
-      <c r="Q5" s="183" t="s">
+      <c r="Q5" s="179" t="s">
         <v>10</v>
       </c>
       <c r="R5" s="180"/>
-      <c r="S5" s="183" t="s">
+      <c r="S5" s="179" t="s">
         <v>11</v>
       </c>
       <c r="T5" s="180"/>
-      <c r="U5" s="183" t="s">
+      <c r="U5" s="179" t="s">
         <v>12</v>
       </c>
       <c r="V5" s="180"/>
-      <c r="W5" s="183" t="s">
+      <c r="W5" s="179" t="s">
         <v>13</v>
       </c>
       <c r="X5" s="180"/>
-      <c r="Y5" s="183" t="s">
+      <c r="Y5" s="179" t="s">
         <v>14</v>
       </c>
       <c r="Z5" s="180"/>
-      <c r="AA5" s="183" t="s">
+      <c r="AA5" s="179" t="s">
         <v>15</v>
       </c>
       <c r="AB5" s="180"/>
-      <c r="AC5" s="183" t="s">
+      <c r="AC5" s="179" t="s">
         <v>16</v>
       </c>
       <c r="AD5" s="180"/>
-      <c r="AE5" s="183" t="s">
+      <c r="AE5" s="179" t="s">
         <v>17</v>
       </c>
       <c r="AF5" s="180"/>
-      <c r="AG5" s="183" t="s">
+      <c r="AG5" s="179" t="s">
         <v>18</v>
       </c>
       <c r="AH5" s="180"/>
-      <c r="AI5" s="183" t="s">
+      <c r="AI5" s="179" t="s">
         <v>19</v>
       </c>
       <c r="AJ5" s="180"/>
-      <c r="AK5" s="183" t="s">
+      <c r="AK5" s="179" t="s">
         <v>20</v>
       </c>
       <c r="AL5" s="180"/>
-      <c r="AM5" s="184" t="s">
+      <c r="AM5" s="188" t="s">
         <v>21</v>
       </c>
       <c r="AN5" s="180"/>
-      <c r="AO5" s="183" t="s">
+      <c r="AO5" s="179" t="s">
         <v>22</v>
       </c>
       <c r="AP5" s="180"/>
-      <c r="AQ5" s="183" t="s">
+      <c r="AQ5" s="179" t="s">
         <v>23</v>
       </c>
       <c r="AR5" s="180"/>
       <c r="AS5" s="2"/>
     </row>
     <row r="6" spans="1:45" ht="12.75" customHeight="1">
-      <c r="A6" s="182"/>
+      <c r="A6" s="187"/>
       <c r="B6" s="8"/>
-      <c r="C6" s="182"/>
+      <c r="C6" s="187"/>
       <c r="D6" s="8"/>
       <c r="E6" s="9" t="s">
         <v>24</v>
@@ -3067,57 +3067,57 @@
         <v>26</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="178" t="s">
+      <c r="E7" s="184" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="179"/>
-      <c r="G7" s="179"/>
-      <c r="H7" s="179"/>
-      <c r="I7" s="179"/>
+      <c r="F7" s="185"/>
+      <c r="G7" s="185"/>
+      <c r="H7" s="185"/>
+      <c r="I7" s="185"/>
       <c r="J7" s="180"/>
-      <c r="K7" s="178" t="s">
+      <c r="K7" s="184" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="179"/>
-      <c r="M7" s="179"/>
+      <c r="L7" s="185"/>
+      <c r="M7" s="185"/>
       <c r="N7" s="180"/>
-      <c r="O7" s="178" t="s">
+      <c r="O7" s="184" t="s">
         <v>29</v>
       </c>
       <c r="P7" s="180"/>
-      <c r="Q7" s="178" t="s">
+      <c r="Q7" s="184" t="s">
         <v>30</v>
       </c>
-      <c r="R7" s="179"/>
-      <c r="S7" s="179"/>
-      <c r="T7" s="179"/>
-      <c r="U7" s="179"/>
-      <c r="V7" s="179"/>
-      <c r="W7" s="179"/>
-      <c r="X7" s="179"/>
-      <c r="Y7" s="179"/>
-      <c r="Z7" s="179"/>
-      <c r="AA7" s="179"/>
+      <c r="R7" s="185"/>
+      <c r="S7" s="185"/>
+      <c r="T7" s="185"/>
+      <c r="U7" s="185"/>
+      <c r="V7" s="185"/>
+      <c r="W7" s="185"/>
+      <c r="X7" s="185"/>
+      <c r="Y7" s="185"/>
+      <c r="Z7" s="185"/>
+      <c r="AA7" s="185"/>
       <c r="AB7" s="180"/>
-      <c r="AC7" s="178" t="s">
+      <c r="AC7" s="184" t="s">
         <v>31</v>
       </c>
-      <c r="AD7" s="179"/>
-      <c r="AE7" s="179"/>
-      <c r="AF7" s="179"/>
-      <c r="AG7" s="179"/>
-      <c r="AH7" s="179"/>
-      <c r="AI7" s="179"/>
-      <c r="AJ7" s="179"/>
-      <c r="AK7" s="179"/>
+      <c r="AD7" s="185"/>
+      <c r="AE7" s="185"/>
+      <c r="AF7" s="185"/>
+      <c r="AG7" s="185"/>
+      <c r="AH7" s="185"/>
+      <c r="AI7" s="185"/>
+      <c r="AJ7" s="185"/>
+      <c r="AK7" s="185"/>
       <c r="AL7" s="180"/>
-      <c r="AM7" s="178" t="s">
+      <c r="AM7" s="184" t="s">
         <v>32</v>
       </c>
-      <c r="AN7" s="179"/>
-      <c r="AO7" s="179"/>
-      <c r="AP7" s="179"/>
-      <c r="AQ7" s="179"/>
+      <c r="AN7" s="185"/>
+      <c r="AO7" s="185"/>
+      <c r="AP7" s="185"/>
+      <c r="AQ7" s="185"/>
       <c r="AR7" s="180"/>
       <c r="AS7" s="2"/>
     </row>
@@ -3130,7 +3130,7 @@
       <c r="D8" s="14"/>
       <c r="E8" s="15">
         <f>E9+E24+E32+E41+E50+E61+E70+E79</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" s="16">
         <v>7</v>
@@ -3446,7 +3446,7 @@
       <c r="J10" s="48">
         <v>0</v>
       </c>
-      <c r="K10" s="176">
+      <c r="K10" s="189">
         <v>1</v>
       </c>
       <c r="L10" s="47">
@@ -3546,7 +3546,7 @@
       <c r="J11" s="48">
         <v>0</v>
       </c>
-      <c r="K11" s="174"/>
+      <c r="K11" s="168"/>
       <c r="L11" s="47">
         <v>0</v>
       </c>
@@ -3636,7 +3636,7 @@
       <c r="J12" s="48">
         <v>0</v>
       </c>
-      <c r="K12" s="175"/>
+      <c r="K12" s="169"/>
       <c r="L12" s="47">
         <v>0</v>
       </c>
@@ -3736,7 +3736,7 @@
       <c r="J13" s="48">
         <v>0</v>
       </c>
-      <c r="K13" s="176">
+      <c r="K13" s="189">
         <v>1</v>
       </c>
       <c r="L13" s="47">
@@ -3826,7 +3826,7 @@
       <c r="J14" s="48">
         <v>0</v>
       </c>
-      <c r="K14" s="175"/>
+      <c r="K14" s="169"/>
       <c r="L14" s="47">
         <v>0</v>
       </c>
@@ -3912,7 +3912,7 @@
       <c r="J15" s="48">
         <v>0</v>
       </c>
-      <c r="K15" s="176">
+      <c r="K15" s="189">
         <v>1</v>
       </c>
       <c r="L15" s="47">
@@ -3922,7 +3922,7 @@
       <c r="N15" s="48">
         <v>0</v>
       </c>
-      <c r="O15" s="173">
+      <c r="O15" s="167">
         <v>1</v>
       </c>
       <c r="P15" s="48">
@@ -4004,7 +4004,7 @@
       <c r="J16" s="48">
         <v>0</v>
       </c>
-      <c r="K16" s="175"/>
+      <c r="K16" s="169"/>
       <c r="L16" s="47">
         <v>0</v>
       </c>
@@ -4012,7 +4012,7 @@
       <c r="N16" s="48">
         <v>0</v>
       </c>
-      <c r="O16" s="175"/>
+      <c r="O16" s="169"/>
       <c r="P16" s="48">
         <v>0</v>
       </c>
@@ -4106,13 +4106,13 @@
       <c r="J17" s="48">
         <v>0</v>
       </c>
-      <c r="K17" s="176">
+      <c r="K17" s="189">
         <v>1</v>
       </c>
       <c r="L17" s="47">
         <v>0</v>
       </c>
-      <c r="M17" s="177">
+      <c r="M17" s="190">
         <v>1</v>
       </c>
       <c r="N17" s="48">
@@ -4204,11 +4204,11 @@
       <c r="J18" s="48">
         <v>0</v>
       </c>
-      <c r="K18" s="175"/>
+      <c r="K18" s="169"/>
       <c r="L18" s="47">
         <v>0</v>
       </c>
-      <c r="M18" s="163"/>
+      <c r="M18" s="176"/>
       <c r="N18" s="48">
         <v>0</v>
       </c>
@@ -5266,7 +5266,7 @@
       <c r="J28" s="81">
         <v>0</v>
       </c>
-      <c r="K28" s="170">
+      <c r="K28" s="161">
         <v>1</v>
       </c>
       <c r="L28" s="80">
@@ -5278,7 +5278,7 @@
       <c r="N28" s="81">
         <v>0</v>
       </c>
-      <c r="O28" s="173">
+      <c r="O28" s="167">
         <v>1</v>
       </c>
       <c r="P28" s="81">
@@ -5368,15 +5368,15 @@
       <c r="J29" s="81">
         <v>0</v>
       </c>
-      <c r="K29" s="172"/>
+      <c r="K29" s="163"/>
       <c r="L29" s="80">
         <v>0</v>
       </c>
-      <c r="M29" s="165"/>
+      <c r="M29" s="166"/>
       <c r="N29" s="81">
         <v>0</v>
       </c>
-      <c r="O29" s="175"/>
+      <c r="O29" s="169"/>
       <c r="P29" s="81">
         <v>0</v>
       </c>
@@ -5464,13 +5464,13 @@
       <c r="J30" s="81">
         <v>0</v>
       </c>
-      <c r="K30" s="166">
+      <c r="K30" s="172">
         <v>1</v>
       </c>
       <c r="L30" s="80">
         <v>0</v>
       </c>
-      <c r="M30" s="168">
+      <c r="M30" s="191">
         <v>1</v>
       </c>
       <c r="N30" s="81">
@@ -5562,11 +5562,11 @@
       <c r="J31" s="68">
         <v>0</v>
       </c>
-      <c r="K31" s="167"/>
+      <c r="K31" s="173"/>
       <c r="L31" s="67">
         <v>0</v>
       </c>
-      <c r="M31" s="169"/>
+      <c r="M31" s="192"/>
       <c r="N31" s="68">
         <v>0</v>
       </c>
@@ -5789,7 +5789,7 @@
       <c r="J33" s="81">
         <v>0</v>
       </c>
-      <c r="K33" s="170">
+      <c r="K33" s="161">
         <v>1</v>
       </c>
       <c r="L33" s="80">
@@ -5879,7 +5879,7 @@
       <c r="H34" s="80"/>
       <c r="I34" s="79"/>
       <c r="J34" s="81"/>
-      <c r="K34" s="171"/>
+      <c r="K34" s="162"/>
       <c r="L34" s="80"/>
       <c r="M34" s="79"/>
       <c r="N34" s="81"/>
@@ -5939,7 +5939,7 @@
       <c r="J35" s="81">
         <v>0</v>
       </c>
-      <c r="K35" s="172"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="80">
         <v>0</v>
       </c>
@@ -6029,7 +6029,7 @@
       <c r="J36" s="81">
         <v>0</v>
       </c>
-      <c r="K36" s="170">
+      <c r="K36" s="161">
         <v>1</v>
       </c>
       <c r="L36" s="80">
@@ -6039,7 +6039,7 @@
       <c r="N36" s="81">
         <v>0</v>
       </c>
-      <c r="O36" s="173">
+      <c r="O36" s="167">
         <v>1</v>
       </c>
       <c r="P36" s="81">
@@ -6121,7 +6121,7 @@
       <c r="J37" s="81">
         <v>0</v>
       </c>
-      <c r="K37" s="171"/>
+      <c r="K37" s="162"/>
       <c r="L37" s="80">
         <v>0</v>
       </c>
@@ -6129,7 +6129,7 @@
       <c r="N37" s="81">
         <v>0</v>
       </c>
-      <c r="O37" s="174"/>
+      <c r="O37" s="168"/>
       <c r="P37" s="81">
         <v>0</v>
       </c>
@@ -6219,7 +6219,7 @@
       <c r="J38" s="81">
         <v>0</v>
       </c>
-      <c r="K38" s="172"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="80">
         <v>0</v>
       </c>
@@ -6227,7 +6227,7 @@
       <c r="N38" s="81">
         <v>0</v>
       </c>
-      <c r="O38" s="175"/>
+      <c r="O38" s="169"/>
       <c r="P38" s="81">
         <v>0</v>
       </c>
@@ -6548,7 +6548,7 @@
         <f>SUM(S42:S49)</f>
         <v>1</v>
       </c>
-      <c r="T41" s="161">
+      <c r="T41" s="174">
         <v>2</v>
       </c>
       <c r="U41" s="32">
@@ -6665,7 +6665,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="79"/>
-      <c r="T42" s="162"/>
+      <c r="T42" s="175"/>
       <c r="U42" s="79">
         <v>1</v>
       </c>
@@ -6765,7 +6765,7 @@
       <c r="S43" s="79">
         <v>1</v>
       </c>
-      <c r="T43" s="162"/>
+      <c r="T43" s="175"/>
       <c r="U43" s="79"/>
       <c r="V43" s="80">
         <v>0</v>
@@ -6847,7 +6847,7 @@
       <c r="Q44" s="84"/>
       <c r="R44" s="80"/>
       <c r="S44" s="79"/>
-      <c r="T44" s="162"/>
+      <c r="T44" s="175"/>
       <c r="U44" s="79"/>
       <c r="V44" s="80"/>
       <c r="W44" s="79"/>
@@ -6902,7 +6902,7 @@
       <c r="L45" s="80">
         <v>0</v>
       </c>
-      <c r="M45" s="165"/>
+      <c r="M45" s="166"/>
       <c r="N45" s="81">
         <v>0</v>
       </c>
@@ -6917,7 +6917,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="79"/>
-      <c r="T45" s="162"/>
+      <c r="T45" s="175"/>
       <c r="U45" s="79"/>
       <c r="V45" s="80">
         <v>0</v>
@@ -7005,7 +7005,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="79"/>
-      <c r="T46" s="162"/>
+      <c r="T46" s="175"/>
       <c r="U46" s="79"/>
       <c r="V46" s="80">
         <v>0</v>
@@ -7080,7 +7080,7 @@
       <c r="J47" s="81">
         <v>0</v>
       </c>
-      <c r="K47" s="170">
+      <c r="K47" s="161">
         <v>1</v>
       </c>
       <c r="L47" s="80">
@@ -7105,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="S47" s="79"/>
-      <c r="T47" s="162"/>
+      <c r="T47" s="175"/>
       <c r="U47" s="79"/>
       <c r="V47" s="80">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       <c r="J48" s="81">
         <v>0</v>
       </c>
-      <c r="K48" s="172"/>
+      <c r="K48" s="163"/>
       <c r="L48" s="80">
         <v>0</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="79"/>
-      <c r="T48" s="162"/>
+      <c r="T48" s="175"/>
       <c r="U48" s="79">
         <v>1</v>
       </c>
@@ -7283,7 +7283,7 @@
         <v>0</v>
       </c>
       <c r="S49" s="66"/>
-      <c r="T49" s="162"/>
+      <c r="T49" s="175"/>
       <c r="U49" s="66"/>
       <c r="V49" s="67">
         <v>0</v>
@@ -7391,7 +7391,7 @@
         <f>SUM(S51:S60)</f>
         <v>4</v>
       </c>
-      <c r="T50" s="163"/>
+      <c r="T50" s="176"/>
       <c r="U50" s="32">
         <f>SUM(U51:U60)</f>
         <v>0</v>
@@ -7498,7 +7498,7 @@
       <c r="J51" s="81">
         <v>0</v>
       </c>
-      <c r="K51" s="170">
+      <c r="K51" s="161">
         <v>1</v>
       </c>
       <c r="L51" s="80">
@@ -7510,7 +7510,7 @@
       <c r="N51" s="81">
         <v>0</v>
       </c>
-      <c r="O51" s="173">
+      <c r="O51" s="167">
         <v>1</v>
       </c>
       <c r="P51" s="81">
@@ -7592,15 +7592,15 @@
       <c r="J52" s="81">
         <v>0</v>
       </c>
-      <c r="K52" s="171"/>
+      <c r="K52" s="162"/>
       <c r="L52" s="80">
         <v>0</v>
       </c>
-      <c r="M52" s="192"/>
+      <c r="M52" s="165"/>
       <c r="N52" s="81">
         <v>0</v>
       </c>
-      <c r="O52" s="174"/>
+      <c r="O52" s="168"/>
       <c r="P52" s="81">
         <v>0</v>
       </c>
@@ -7686,15 +7686,15 @@
       <c r="J53" s="81">
         <v>0</v>
       </c>
-      <c r="K53" s="172"/>
+      <c r="K53" s="163"/>
       <c r="L53" s="80">
         <v>0</v>
       </c>
-      <c r="M53" s="165"/>
+      <c r="M53" s="166"/>
       <c r="N53" s="81">
         <v>0</v>
       </c>
-      <c r="O53" s="175"/>
+      <c r="O53" s="169"/>
       <c r="P53" s="81">
         <v>0</v>
       </c>
@@ -8002,7 +8002,7 @@
       <c r="J56" s="81">
         <v>0</v>
       </c>
-      <c r="K56" s="170">
+      <c r="K56" s="161">
         <v>1</v>
       </c>
       <c r="L56" s="80">
@@ -8094,7 +8094,7 @@
       <c r="J57" s="81">
         <v>0</v>
       </c>
-      <c r="K57" s="172"/>
+      <c r="K57" s="163"/>
       <c r="L57" s="80">
         <v>0</v>
       </c>
@@ -8280,7 +8280,7 @@
       <c r="J59" s="81">
         <v>0</v>
       </c>
-      <c r="K59" s="166">
+      <c r="K59" s="172">
         <v>1</v>
       </c>
       <c r="L59" s="80">
@@ -8376,7 +8376,7 @@
       <c r="J60" s="68">
         <v>0</v>
       </c>
-      <c r="K60" s="167"/>
+      <c r="K60" s="173"/>
       <c r="L60" s="67">
         <v>0</v>
       </c>
@@ -8451,7 +8451,7 @@
       <c r="D61" s="74"/>
       <c r="E61" s="30">
         <f>SUM(E62:E69)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" s="31">
         <v>1</v>
@@ -8496,7 +8496,7 @@
         <f>SUM(Q62:Q69)</f>
         <v>6</v>
       </c>
-      <c r="R61" s="161">
+      <c r="R61" s="174">
         <v>2</v>
       </c>
       <c r="S61" s="32">
@@ -8635,7 +8635,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="84"/>
-      <c r="R62" s="162"/>
+      <c r="R62" s="175"/>
       <c r="S62" s="79"/>
       <c r="T62" s="80">
         <v>0</v>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="D63" s="44"/>
       <c r="E63" s="78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" s="79">
         <v>0</v>
@@ -8745,7 +8745,7 @@
       <c r="Q63" s="84">
         <v>1</v>
       </c>
-      <c r="R63" s="162"/>
+      <c r="R63" s="175"/>
       <c r="S63" s="79">
         <v>1</v>
       </c>
@@ -8845,7 +8845,7 @@
       <c r="Q64" s="84">
         <v>1</v>
       </c>
-      <c r="R64" s="162"/>
+      <c r="R64" s="175"/>
       <c r="S64" s="79"/>
       <c r="T64" s="80">
         <v>0</v>
@@ -8951,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="Q65" s="84"/>
-      <c r="R65" s="162"/>
+      <c r="R65" s="175"/>
       <c r="S65" s="79"/>
       <c r="T65" s="80">
         <v>0</v>
@@ -9057,7 +9057,7 @@
       <c r="Q66" s="84">
         <v>2</v>
       </c>
-      <c r="R66" s="162"/>
+      <c r="R66" s="175"/>
       <c r="S66" s="79">
         <v>2</v>
       </c>
@@ -9150,7 +9150,7 @@
       <c r="J67" s="81">
         <v>0</v>
       </c>
-      <c r="K67" s="170">
+      <c r="K67" s="161">
         <v>1</v>
       </c>
       <c r="L67" s="80">
@@ -9169,7 +9169,7 @@
       <c r="Q67" s="84">
         <v>1</v>
       </c>
-      <c r="R67" s="162"/>
+      <c r="R67" s="175"/>
       <c r="S67" s="79">
         <v>1</v>
       </c>
@@ -9248,11 +9248,11 @@
       <c r="J68" s="81">
         <v>0</v>
       </c>
-      <c r="K68" s="172"/>
+      <c r="K68" s="163"/>
       <c r="L68" s="80">
         <v>0</v>
       </c>
-      <c r="M68" s="165"/>
+      <c r="M68" s="166"/>
       <c r="N68" s="81">
         <v>0</v>
       </c>
@@ -9265,7 +9265,7 @@
       <c r="Q68" s="84">
         <v>1</v>
       </c>
-      <c r="R68" s="162"/>
+      <c r="R68" s="175"/>
       <c r="S68" s="79"/>
       <c r="T68" s="80">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>0</v>
       </c>
       <c r="Q69" s="70"/>
-      <c r="R69" s="162"/>
+      <c r="R69" s="175"/>
       <c r="S69" s="66"/>
       <c r="T69" s="67">
         <v>0</v>
@@ -9464,7 +9464,7 @@
         <f>SUM(Q71:Q78)</f>
         <v>1</v>
       </c>
-      <c r="R70" s="163"/>
+      <c r="R70" s="176"/>
       <c r="S70" s="32">
         <f>SUM(S71:S78)</f>
         <v>2</v>
@@ -9583,7 +9583,7 @@
       <c r="J71" s="81">
         <v>0</v>
       </c>
-      <c r="K71" s="170">
+      <c r="K71" s="161">
         <v>1</v>
       </c>
       <c r="L71" s="80">
@@ -9677,7 +9677,7 @@
       <c r="J72" s="81">
         <v>0</v>
       </c>
-      <c r="K72" s="171"/>
+      <c r="K72" s="162"/>
       <c r="L72" s="80">
         <v>0</v>
       </c>
@@ -9767,7 +9767,7 @@
       <c r="J73" s="81">
         <v>0</v>
       </c>
-      <c r="K73" s="172"/>
+      <c r="K73" s="163"/>
       <c r="L73" s="80">
         <v>0</v>
       </c>
@@ -9871,7 +9871,7 @@
       <c r="N74" s="81">
         <v>0</v>
       </c>
-      <c r="O74" s="173">
+      <c r="O74" s="167">
         <v>1</v>
       </c>
       <c r="P74" s="81">
@@ -9971,7 +9971,7 @@
       <c r="N75" s="81">
         <v>0</v>
       </c>
-      <c r="O75" s="175"/>
+      <c r="O75" s="169"/>
       <c r="P75" s="81">
         <v>0</v>
       </c>
@@ -10053,7 +10053,7 @@
       <c r="J76" s="81">
         <v>0</v>
       </c>
-      <c r="K76" s="170">
+      <c r="K76" s="161">
         <v>1</v>
       </c>
       <c r="L76" s="80">
@@ -10147,7 +10147,7 @@
       <c r="J77" s="81">
         <v>0</v>
       </c>
-      <c r="K77" s="172"/>
+      <c r="K77" s="163"/>
       <c r="L77" s="80">
         <v>0</v>
       </c>
@@ -11019,7 +11019,7 @@
       <c r="J85" s="112">
         <v>0</v>
       </c>
-      <c r="K85" s="189">
+      <c r="K85" s="181">
         <v>1</v>
       </c>
       <c r="L85" s="79">
@@ -11129,11 +11129,11 @@
       <c r="J86" s="127">
         <v>0</v>
       </c>
-      <c r="K86" s="190"/>
+      <c r="K86" s="182"/>
       <c r="L86" s="91">
         <v>0</v>
       </c>
-      <c r="M86" s="191"/>
+      <c r="M86" s="183"/>
       <c r="N86" s="127">
         <v>0</v>
       </c>
@@ -11363,86 +11363,86 @@
       <c r="B89" s="140"/>
       <c r="C89" s="140"/>
       <c r="D89" s="140"/>
-      <c r="E89" s="185" t="s">
+      <c r="E89" s="177" t="s">
         <v>114</v>
       </c>
-      <c r="F89" s="186"/>
-      <c r="G89" s="185" t="s">
+      <c r="F89" s="171"/>
+      <c r="G89" s="177" t="s">
         <v>115</v>
       </c>
-      <c r="H89" s="186"/>
-      <c r="I89" s="185" t="s">
+      <c r="H89" s="171"/>
+      <c r="I89" s="177" t="s">
         <v>116</v>
       </c>
-      <c r="J89" s="186"/>
-      <c r="K89" s="185" t="s">
+      <c r="J89" s="171"/>
+      <c r="K89" s="177" t="s">
         <v>117</v>
       </c>
-      <c r="L89" s="186"/>
-      <c r="M89" s="188" t="s">
+      <c r="L89" s="171"/>
+      <c r="M89" s="178" t="s">
         <v>118</v>
       </c>
-      <c r="N89" s="186"/>
-      <c r="O89" s="188" t="s">
+      <c r="N89" s="171"/>
+      <c r="O89" s="178" t="s">
         <v>119</v>
       </c>
-      <c r="P89" s="186"/>
-      <c r="Q89" s="187" t="s">
+      <c r="P89" s="171"/>
+      <c r="Q89" s="170" t="s">
         <v>120</v>
       </c>
-      <c r="R89" s="186"/>
-      <c r="S89" s="187" t="s">
+      <c r="R89" s="171"/>
+      <c r="S89" s="170" t="s">
         <v>121</v>
       </c>
-      <c r="T89" s="186"/>
-      <c r="U89" s="187" t="s">
+      <c r="T89" s="171"/>
+      <c r="U89" s="170" t="s">
         <v>122</v>
       </c>
-      <c r="V89" s="186"/>
-      <c r="W89" s="187" t="s">
+      <c r="V89" s="171"/>
+      <c r="W89" s="170" t="s">
         <v>123</v>
       </c>
-      <c r="X89" s="186"/>
-      <c r="Y89" s="187" t="s">
+      <c r="X89" s="171"/>
+      <c r="Y89" s="170" t="s">
         <v>124</v>
       </c>
-      <c r="Z89" s="186"/>
-      <c r="AA89" s="187" t="s">
+      <c r="Z89" s="171"/>
+      <c r="AA89" s="170" t="s">
         <v>122</v>
       </c>
-      <c r="AB89" s="186"/>
-      <c r="AC89" s="188" t="s">
+      <c r="AB89" s="171"/>
+      <c r="AC89" s="178" t="s">
         <v>125</v>
       </c>
-      <c r="AD89" s="186"/>
-      <c r="AE89" s="188" t="s">
+      <c r="AD89" s="171"/>
+      <c r="AE89" s="178" t="s">
         <v>126</v>
       </c>
-      <c r="AF89" s="186"/>
-      <c r="AG89" s="188" t="s">
+      <c r="AF89" s="171"/>
+      <c r="AG89" s="178" t="s">
         <v>127</v>
       </c>
-      <c r="AH89" s="186"/>
-      <c r="AI89" s="188" t="s">
+      <c r="AH89" s="171"/>
+      <c r="AI89" s="178" t="s">
         <v>127</v>
       </c>
-      <c r="AJ89" s="186"/>
-      <c r="AK89" s="188" t="s">
+      <c r="AJ89" s="171"/>
+      <c r="AK89" s="178" t="s">
         <v>128</v>
       </c>
-      <c r="AL89" s="186"/>
-      <c r="AM89" s="185" t="s">
+      <c r="AL89" s="171"/>
+      <c r="AM89" s="177" t="s">
         <v>129</v>
       </c>
-      <c r="AN89" s="186"/>
-      <c r="AO89" s="185" t="s">
+      <c r="AN89" s="171"/>
+      <c r="AO89" s="177" t="s">
         <v>130</v>
       </c>
-      <c r="AP89" s="186"/>
-      <c r="AQ89" s="185" t="s">
+      <c r="AP89" s="171"/>
+      <c r="AQ89" s="177" t="s">
         <v>131</v>
       </c>
-      <c r="AR89" s="186"/>
+      <c r="AR89" s="171"/>
       <c r="AS89" s="141"/>
     </row>
     <row r="90" spans="1:45" ht="12.75" customHeight="1">
@@ -54351,25 +54351,49 @@
   </sheetData>
   <autoFilter ref="E6:AR87" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="78">
-    <mergeCell ref="K51:K53"/>
-    <mergeCell ref="M51:M53"/>
-    <mergeCell ref="O51:O53"/>
-    <mergeCell ref="K56:K57"/>
-    <mergeCell ref="Y89:Z89"/>
-    <mergeCell ref="K59:K60"/>
-    <mergeCell ref="R61:R70"/>
-    <mergeCell ref="K67:K68"/>
-    <mergeCell ref="M67:M68"/>
-    <mergeCell ref="K71:K73"/>
-    <mergeCell ref="AQ89:AR89"/>
-    <mergeCell ref="AA89:AB89"/>
-    <mergeCell ref="AC89:AD89"/>
-    <mergeCell ref="AE89:AF89"/>
-    <mergeCell ref="AG89:AH89"/>
-    <mergeCell ref="AI89:AJ89"/>
-    <mergeCell ref="AK89:AL89"/>
-    <mergeCell ref="AM89:AN89"/>
-    <mergeCell ref="AO89:AP89"/>
+    <mergeCell ref="T41:T50"/>
+    <mergeCell ref="M44:M45"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="K33:K35"/>
+    <mergeCell ref="K36:K38"/>
+    <mergeCell ref="O36:O38"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="M28:M29"/>
+    <mergeCell ref="O28:O29"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="AM7:AR7"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="E7:J7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="Q7:AB7"/>
+    <mergeCell ref="AC7:AL7"/>
+    <mergeCell ref="AM5:AN5"/>
+    <mergeCell ref="AO5:AP5"/>
+    <mergeCell ref="AQ5:AR5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AC5:AD5"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="AG5:AH5"/>
     <mergeCell ref="AI5:AJ5"/>
     <mergeCell ref="AK5:AL5"/>
     <mergeCell ref="G89:H89"/>
@@ -54386,49 +54410,25 @@
     <mergeCell ref="M89:N89"/>
     <mergeCell ref="U89:V89"/>
     <mergeCell ref="W89:X89"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="AC5:AD5"/>
-    <mergeCell ref="AE5:AF5"/>
-    <mergeCell ref="AG5:AH5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="AM7:AR7"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="E7:J7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="Q7:AB7"/>
-    <mergeCell ref="AC7:AL7"/>
-    <mergeCell ref="AM5:AN5"/>
-    <mergeCell ref="AO5:AP5"/>
-    <mergeCell ref="AQ5:AR5"/>
-    <mergeCell ref="M28:M29"/>
-    <mergeCell ref="O28:O29"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="K28:K29"/>
-    <mergeCell ref="T41:T50"/>
-    <mergeCell ref="M44:M45"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="K33:K35"/>
-    <mergeCell ref="K36:K38"/>
-    <mergeCell ref="O36:O38"/>
-    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="AQ89:AR89"/>
+    <mergeCell ref="AA89:AB89"/>
+    <mergeCell ref="AC89:AD89"/>
+    <mergeCell ref="AE89:AF89"/>
+    <mergeCell ref="AG89:AH89"/>
+    <mergeCell ref="AI89:AJ89"/>
+    <mergeCell ref="AK89:AL89"/>
+    <mergeCell ref="AM89:AN89"/>
+    <mergeCell ref="AO89:AP89"/>
+    <mergeCell ref="K51:K53"/>
+    <mergeCell ref="M51:M53"/>
+    <mergeCell ref="O51:O53"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="Y89:Z89"/>
+    <mergeCell ref="K59:K60"/>
+    <mergeCell ref="R61:R70"/>
+    <mergeCell ref="K67:K68"/>
+    <mergeCell ref="M67:M68"/>
+    <mergeCell ref="K71:K73"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:AR8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
@@ -54459,7 +54459,7 @@
       <c r="C1" s="151"/>
     </row>
     <row r="2" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A2" s="195" t="s">
+      <c r="A2" s="193" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="152" t="s">
@@ -54509,7 +54509,7 @@
       <c r="AP2" s="154"/>
     </row>
     <row r="3" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A3" s="182"/>
+      <c r="A3" s="187"/>
       <c r="B3" s="156" t="s">
         <v>25</v>
       </c>
@@ -54521,7 +54521,7 @@
       </c>
     </row>
     <row r="4" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A4" s="195" t="s">
+      <c r="A4" s="193" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="156" t="s">
@@ -54532,7 +54532,7 @@
       </c>
     </row>
     <row r="5" spans="1:42" ht="14.4">
-      <c r="A5" s="182"/>
+      <c r="A5" s="187"/>
       <c r="B5" s="156" t="s">
         <v>25</v>
       </c>
@@ -54544,7 +54544,7 @@
       </c>
     </row>
     <row r="6" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A6" s="195" t="s">
+      <c r="A6" s="193" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="156" t="s">
@@ -54555,20 +54555,20 @@
       </c>
     </row>
     <row r="7" spans="1:42" ht="14.4">
-      <c r="A7" s="182"/>
+      <c r="A7" s="187"/>
       <c r="B7" s="156" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="153">
         <v>8</v>
       </c>
-      <c r="D7" s="200" t="s">
+      <c r="D7" s="194" t="s">
         <v>116</v>
       </c>
-      <c r="E7" s="201"/>
+      <c r="E7" s="195"/>
     </row>
     <row r="8" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A8" s="195" t="s">
+      <c r="A8" s="193" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="156" t="s">
@@ -54579,7 +54579,7 @@
       </c>
     </row>
     <row r="9" spans="1:42" ht="14.4">
-      <c r="A9" s="182"/>
+      <c r="A9" s="187"/>
       <c r="B9" s="156" t="s">
         <v>25</v>
       </c>
@@ -54591,7 +54591,7 @@
       </c>
     </row>
     <row r="10" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A10" s="195" t="s">
+      <c r="A10" s="193" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="156" t="s">
@@ -54602,7 +54602,7 @@
       </c>
     </row>
     <row r="11" spans="1:42" ht="14.4">
-      <c r="A11" s="182"/>
+      <c r="A11" s="187"/>
       <c r="B11" s="156" t="s">
         <v>25</v>
       </c>
@@ -54614,7 +54614,7 @@
       </c>
     </row>
     <row r="12" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A12" s="195" t="s">
+      <c r="A12" s="193" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="156" t="s">
@@ -54625,7 +54625,7 @@
       </c>
     </row>
     <row r="13" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A13" s="182"/>
+      <c r="A13" s="187"/>
       <c r="B13" s="156" t="s">
         <v>25</v>
       </c>
@@ -54637,7 +54637,7 @@
       </c>
     </row>
     <row r="14" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A14" s="195" t="s">
+      <c r="A14" s="193" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="156" t="s">
@@ -54648,7 +54648,7 @@
       </c>
     </row>
     <row r="15" spans="1:42" ht="14.4">
-      <c r="A15" s="182"/>
+      <c r="A15" s="187"/>
       <c r="B15" s="156" t="s">
         <v>25</v>
       </c>
@@ -54660,7 +54660,7 @@
       </c>
     </row>
     <row r="16" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A16" s="195" t="s">
+      <c r="A16" s="193" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="156" t="s">
@@ -54671,7 +54671,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A17" s="182"/>
+      <c r="A17" s="187"/>
       <c r="B17" s="156" t="s">
         <v>25</v>
       </c>
@@ -54680,7 +54680,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A18" s="195" t="s">
+      <c r="A18" s="193" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="156" t="s">
@@ -54691,7 +54691,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A19" s="182"/>
+      <c r="A19" s="187"/>
       <c r="B19" s="156" t="s">
         <v>25</v>
       </c>
@@ -54700,7 +54700,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A20" s="195" t="s">
+      <c r="A20" s="193" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="156" t="s">
@@ -54711,7 +54711,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A21" s="182"/>
+      <c r="A21" s="187"/>
       <c r="B21" s="156" t="s">
         <v>25</v>
       </c>
@@ -54720,7 +54720,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A22" s="195" t="s">
+      <c r="A22" s="193" t="s">
         <v>14</v>
       </c>
       <c r="B22" s="156" t="s">
@@ -54731,7 +54731,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A23" s="182"/>
+      <c r="A23" s="187"/>
       <c r="B23" s="156" t="s">
         <v>25</v>
       </c>
@@ -54740,7 +54740,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A24" s="195" t="s">
+      <c r="A24" s="193" t="s">
         <v>15</v>
       </c>
       <c r="B24" s="156" t="s">
@@ -54751,7 +54751,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A25" s="182"/>
+      <c r="A25" s="187"/>
       <c r="B25" s="156" t="s">
         <v>25</v>
       </c>
@@ -54760,7 +54760,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A26" s="195" t="s">
+      <c r="A26" s="193" t="s">
         <v>16</v>
       </c>
       <c r="B26" s="156" t="s">
@@ -54771,7 +54771,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A27" s="182"/>
+      <c r="A27" s="187"/>
       <c r="B27" s="156" t="s">
         <v>25</v>
       </c>
@@ -54780,7 +54780,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A28" s="195" t="s">
+      <c r="A28" s="193" t="s">
         <v>17</v>
       </c>
       <c r="B28" s="156" t="s">
@@ -54791,7 +54791,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A29" s="182"/>
+      <c r="A29" s="187"/>
       <c r="B29" s="156" t="s">
         <v>25</v>
       </c>
@@ -54800,7 +54800,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A30" s="195" t="s">
+      <c r="A30" s="193" t="s">
         <v>18</v>
       </c>
       <c r="B30" s="156" t="s">
@@ -54811,7 +54811,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A31" s="182"/>
+      <c r="A31" s="187"/>
       <c r="B31" s="156" t="s">
         <v>25</v>
       </c>
@@ -54820,7 +54820,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A32" s="195" t="s">
+      <c r="A32" s="193" t="s">
         <v>19</v>
       </c>
       <c r="B32" s="156" t="s">
@@ -54831,7 +54831,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="22.5" customHeight="1">
-      <c r="A33" s="182"/>
+      <c r="A33" s="187"/>
       <c r="B33" s="156" t="s">
         <v>25</v>
       </c>
@@ -54840,7 +54840,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="22.5" customHeight="1">
-      <c r="A34" s="195" t="s">
+      <c r="A34" s="193" t="s">
         <v>20</v>
       </c>
       <c r="B34" s="156" t="s">
@@ -54851,7 +54851,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="22.5" customHeight="1">
-      <c r="A35" s="182"/>
+      <c r="A35" s="187"/>
       <c r="B35" s="156" t="s">
         <v>25</v>
       </c>
@@ -54860,7 +54860,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="22.5" customHeight="1">
-      <c r="A36" s="196" t="s">
+      <c r="A36" s="198" t="s">
         <v>21</v>
       </c>
       <c r="B36" s="152" t="s">
@@ -54871,20 +54871,20 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="14.4">
-      <c r="A37" s="197"/>
+      <c r="A37" s="199"/>
       <c r="B37" s="156" t="s">
         <v>25</v>
       </c>
       <c r="C37" s="153">
         <v>8</v>
       </c>
-      <c r="D37" s="198" t="s">
+      <c r="D37" s="200" t="s">
         <v>129</v>
       </c>
-      <c r="E37" s="199"/>
+      <c r="E37" s="201"/>
     </row>
     <row r="38" spans="1:5" ht="22.5" customHeight="1">
-      <c r="A38" s="195" t="s">
+      <c r="A38" s="193" t="s">
         <v>22</v>
       </c>
       <c r="B38" s="156" t="s">
@@ -54895,7 +54895,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="14.4">
-      <c r="A39" s="182"/>
+      <c r="A39" s="187"/>
       <c r="B39" s="156" t="s">
         <v>25</v>
       </c>
@@ -54907,7 +54907,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="22.5" customHeight="1">
-      <c r="A40" s="195" t="s">
+      <c r="A40" s="193" t="s">
         <v>23</v>
       </c>
       <c r="B40" s="156" t="s">
@@ -54918,17 +54918,17 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="14.4">
-      <c r="A41" s="182"/>
+      <c r="A41" s="187"/>
       <c r="B41" s="156" t="s">
         <v>25</v>
       </c>
       <c r="C41" s="153">
         <v>8</v>
       </c>
-      <c r="D41" s="193" t="s">
+      <c r="D41" s="196" t="s">
         <v>131</v>
       </c>
-      <c r="E41" s="194"/>
+      <c r="E41" s="197"/>
     </row>
     <row r="42" spans="1:5" ht="14.4">
       <c r="C42" s="151"/>
@@ -57809,21 +57809,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A40:A41"/>
     <mergeCell ref="D41:E41"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A30:A31"/>
@@ -57832,6 +57817,21 @@
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="D37:E37"/>
     <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A8:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DHMT2026 - Phan chia chi tieu tai VCK 20260617.XLSX
+++ b/DHMT2026 - Phan chia chi tieu tai VCK 20260617.XLSX
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ntlon\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\App xep lich thi dau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA706E49-3F9C-4FD2-96AE-9242ACF05B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E43543A-A398-4178-AAD3-727B139B98C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2329,81 +2329,77 @@
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="4" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2412,6 +2408,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2843,100 +2843,100 @@
       <c r="AS4" s="2"/>
     </row>
     <row r="5" spans="1:45" ht="56.25" customHeight="1">
-      <c r="A5" s="186" t="s">
+      <c r="A5" s="181" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="186" t="s">
+      <c r="C5" s="181" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="7"/>
-      <c r="E5" s="179" t="s">
+      <c r="E5" s="183" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="180"/>
-      <c r="G5" s="179" t="s">
+      <c r="G5" s="183" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="180"/>
-      <c r="I5" s="179" t="s">
+      <c r="I5" s="183" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="180"/>
-      <c r="K5" s="179" t="s">
+      <c r="K5" s="183" t="s">
         <v>7</v>
       </c>
       <c r="L5" s="180"/>
-      <c r="M5" s="179" t="s">
+      <c r="M5" s="183" t="s">
         <v>8</v>
       </c>
       <c r="N5" s="180"/>
-      <c r="O5" s="179" t="s">
+      <c r="O5" s="183" t="s">
         <v>9</v>
       </c>
       <c r="P5" s="180"/>
-      <c r="Q5" s="179" t="s">
+      <c r="Q5" s="183" t="s">
         <v>10</v>
       </c>
       <c r="R5" s="180"/>
-      <c r="S5" s="179" t="s">
+      <c r="S5" s="183" t="s">
         <v>11</v>
       </c>
       <c r="T5" s="180"/>
-      <c r="U5" s="179" t="s">
+      <c r="U5" s="183" t="s">
         <v>12</v>
       </c>
       <c r="V5" s="180"/>
-      <c r="W5" s="179" t="s">
+      <c r="W5" s="183" t="s">
         <v>13</v>
       </c>
       <c r="X5" s="180"/>
-      <c r="Y5" s="179" t="s">
+      <c r="Y5" s="183" t="s">
         <v>14</v>
       </c>
       <c r="Z5" s="180"/>
-      <c r="AA5" s="179" t="s">
+      <c r="AA5" s="183" t="s">
         <v>15</v>
       </c>
       <c r="AB5" s="180"/>
-      <c r="AC5" s="179" t="s">
+      <c r="AC5" s="183" t="s">
         <v>16</v>
       </c>
       <c r="AD5" s="180"/>
-      <c r="AE5" s="179" t="s">
+      <c r="AE5" s="183" t="s">
         <v>17</v>
       </c>
       <c r="AF5" s="180"/>
-      <c r="AG5" s="179" t="s">
+      <c r="AG5" s="183" t="s">
         <v>18</v>
       </c>
       <c r="AH5" s="180"/>
-      <c r="AI5" s="179" t="s">
+      <c r="AI5" s="183" t="s">
         <v>19</v>
       </c>
       <c r="AJ5" s="180"/>
-      <c r="AK5" s="179" t="s">
+      <c r="AK5" s="183" t="s">
         <v>20</v>
       </c>
       <c r="AL5" s="180"/>
-      <c r="AM5" s="188" t="s">
+      <c r="AM5" s="184" t="s">
         <v>21</v>
       </c>
       <c r="AN5" s="180"/>
-      <c r="AO5" s="179" t="s">
+      <c r="AO5" s="183" t="s">
         <v>22</v>
       </c>
       <c r="AP5" s="180"/>
-      <c r="AQ5" s="179" t="s">
+      <c r="AQ5" s="183" t="s">
         <v>23</v>
       </c>
       <c r="AR5" s="180"/>
       <c r="AS5" s="2"/>
     </row>
     <row r="6" spans="1:45" ht="12.75" customHeight="1">
-      <c r="A6" s="187"/>
+      <c r="A6" s="182"/>
       <c r="B6" s="8"/>
-      <c r="C6" s="187"/>
+      <c r="C6" s="182"/>
       <c r="D6" s="8"/>
       <c r="E6" s="9" t="s">
         <v>24</v>
@@ -3067,57 +3067,57 @@
         <v>26</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="184" t="s">
+      <c r="E7" s="178" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="185"/>
-      <c r="G7" s="185"/>
-      <c r="H7" s="185"/>
-      <c r="I7" s="185"/>
+      <c r="F7" s="179"/>
+      <c r="G7" s="179"/>
+      <c r="H7" s="179"/>
+      <c r="I7" s="179"/>
       <c r="J7" s="180"/>
-      <c r="K7" s="184" t="s">
+      <c r="K7" s="178" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="185"/>
-      <c r="M7" s="185"/>
+      <c r="L7" s="179"/>
+      <c r="M7" s="179"/>
       <c r="N7" s="180"/>
-      <c r="O7" s="184" t="s">
+      <c r="O7" s="178" t="s">
         <v>29</v>
       </c>
       <c r="P7" s="180"/>
-      <c r="Q7" s="184" t="s">
+      <c r="Q7" s="178" t="s">
         <v>30</v>
       </c>
-      <c r="R7" s="185"/>
-      <c r="S7" s="185"/>
-      <c r="T7" s="185"/>
-      <c r="U7" s="185"/>
-      <c r="V7" s="185"/>
-      <c r="W7" s="185"/>
-      <c r="X7" s="185"/>
-      <c r="Y7" s="185"/>
-      <c r="Z7" s="185"/>
-      <c r="AA7" s="185"/>
+      <c r="R7" s="179"/>
+      <c r="S7" s="179"/>
+      <c r="T7" s="179"/>
+      <c r="U7" s="179"/>
+      <c r="V7" s="179"/>
+      <c r="W7" s="179"/>
+      <c r="X7" s="179"/>
+      <c r="Y7" s="179"/>
+      <c r="Z7" s="179"/>
+      <c r="AA7" s="179"/>
       <c r="AB7" s="180"/>
-      <c r="AC7" s="184" t="s">
+      <c r="AC7" s="178" t="s">
         <v>31</v>
       </c>
-      <c r="AD7" s="185"/>
-      <c r="AE7" s="185"/>
-      <c r="AF7" s="185"/>
-      <c r="AG7" s="185"/>
-      <c r="AH7" s="185"/>
-      <c r="AI7" s="185"/>
-      <c r="AJ7" s="185"/>
-      <c r="AK7" s="185"/>
+      <c r="AD7" s="179"/>
+      <c r="AE7" s="179"/>
+      <c r="AF7" s="179"/>
+      <c r="AG7" s="179"/>
+      <c r="AH7" s="179"/>
+      <c r="AI7" s="179"/>
+      <c r="AJ7" s="179"/>
+      <c r="AK7" s="179"/>
       <c r="AL7" s="180"/>
-      <c r="AM7" s="184" t="s">
+      <c r="AM7" s="178" t="s">
         <v>32</v>
       </c>
-      <c r="AN7" s="185"/>
-      <c r="AO7" s="185"/>
-      <c r="AP7" s="185"/>
-      <c r="AQ7" s="185"/>
+      <c r="AN7" s="179"/>
+      <c r="AO7" s="179"/>
+      <c r="AP7" s="179"/>
+      <c r="AQ7" s="179"/>
       <c r="AR7" s="180"/>
       <c r="AS7" s="2"/>
     </row>
@@ -3130,7 +3130,7 @@
       <c r="D8" s="14"/>
       <c r="E8" s="15">
         <f>E9+E24+E32+E41+E50+E61+E70+E79</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" s="16">
         <v>7</v>
@@ -3446,7 +3446,7 @@
       <c r="J10" s="48">
         <v>0</v>
       </c>
-      <c r="K10" s="189">
+      <c r="K10" s="176">
         <v>1</v>
       </c>
       <c r="L10" s="47">
@@ -3546,7 +3546,7 @@
       <c r="J11" s="48">
         <v>0</v>
       </c>
-      <c r="K11" s="168"/>
+      <c r="K11" s="174"/>
       <c r="L11" s="47">
         <v>0</v>
       </c>
@@ -3636,7 +3636,7 @@
       <c r="J12" s="48">
         <v>0</v>
       </c>
-      <c r="K12" s="169"/>
+      <c r="K12" s="175"/>
       <c r="L12" s="47">
         <v>0</v>
       </c>
@@ -3736,7 +3736,7 @@
       <c r="J13" s="48">
         <v>0</v>
       </c>
-      <c r="K13" s="189">
+      <c r="K13" s="176">
         <v>1</v>
       </c>
       <c r="L13" s="47">
@@ -3826,7 +3826,7 @@
       <c r="J14" s="48">
         <v>0</v>
       </c>
-      <c r="K14" s="169"/>
+      <c r="K14" s="175"/>
       <c r="L14" s="47">
         <v>0</v>
       </c>
@@ -3912,7 +3912,7 @@
       <c r="J15" s="48">
         <v>0</v>
       </c>
-      <c r="K15" s="189">
+      <c r="K15" s="176">
         <v>1</v>
       </c>
       <c r="L15" s="47">
@@ -3922,7 +3922,7 @@
       <c r="N15" s="48">
         <v>0</v>
       </c>
-      <c r="O15" s="167">
+      <c r="O15" s="173">
         <v>1</v>
       </c>
       <c r="P15" s="48">
@@ -4004,7 +4004,7 @@
       <c r="J16" s="48">
         <v>0</v>
       </c>
-      <c r="K16" s="169"/>
+      <c r="K16" s="175"/>
       <c r="L16" s="47">
         <v>0</v>
       </c>
@@ -4012,7 +4012,7 @@
       <c r="N16" s="48">
         <v>0</v>
       </c>
-      <c r="O16" s="169"/>
+      <c r="O16" s="175"/>
       <c r="P16" s="48">
         <v>0</v>
       </c>
@@ -4106,13 +4106,13 @@
       <c r="J17" s="48">
         <v>0</v>
       </c>
-      <c r="K17" s="189">
+      <c r="K17" s="176">
         <v>1</v>
       </c>
       <c r="L17" s="47">
         <v>0</v>
       </c>
-      <c r="M17" s="190">
+      <c r="M17" s="177">
         <v>1</v>
       </c>
       <c r="N17" s="48">
@@ -4204,11 +4204,11 @@
       <c r="J18" s="48">
         <v>0</v>
       </c>
-      <c r="K18" s="169"/>
+      <c r="K18" s="175"/>
       <c r="L18" s="47">
         <v>0</v>
       </c>
-      <c r="M18" s="176"/>
+      <c r="M18" s="163"/>
       <c r="N18" s="48">
         <v>0</v>
       </c>
@@ -5266,7 +5266,7 @@
       <c r="J28" s="81">
         <v>0</v>
       </c>
-      <c r="K28" s="161">
+      <c r="K28" s="170">
         <v>1</v>
       </c>
       <c r="L28" s="80">
@@ -5278,7 +5278,7 @@
       <c r="N28" s="81">
         <v>0</v>
       </c>
-      <c r="O28" s="167">
+      <c r="O28" s="173">
         <v>1</v>
       </c>
       <c r="P28" s="81">
@@ -5368,15 +5368,15 @@
       <c r="J29" s="81">
         <v>0</v>
       </c>
-      <c r="K29" s="163"/>
+      <c r="K29" s="172"/>
       <c r="L29" s="80">
         <v>0</v>
       </c>
-      <c r="M29" s="166"/>
+      <c r="M29" s="165"/>
       <c r="N29" s="81">
         <v>0</v>
       </c>
-      <c r="O29" s="169"/>
+      <c r="O29" s="175"/>
       <c r="P29" s="81">
         <v>0</v>
       </c>
@@ -5464,13 +5464,13 @@
       <c r="J30" s="81">
         <v>0</v>
       </c>
-      <c r="K30" s="172">
+      <c r="K30" s="166">
         <v>1</v>
       </c>
       <c r="L30" s="80">
         <v>0</v>
       </c>
-      <c r="M30" s="191">
+      <c r="M30" s="168">
         <v>1</v>
       </c>
       <c r="N30" s="81">
@@ -5562,11 +5562,11 @@
       <c r="J31" s="68">
         <v>0</v>
       </c>
-      <c r="K31" s="173"/>
+      <c r="K31" s="167"/>
       <c r="L31" s="67">
         <v>0</v>
       </c>
-      <c r="M31" s="192"/>
+      <c r="M31" s="169"/>
       <c r="N31" s="68">
         <v>0</v>
       </c>
@@ -5789,7 +5789,7 @@
       <c r="J33" s="81">
         <v>0</v>
       </c>
-      <c r="K33" s="161">
+      <c r="K33" s="170">
         <v>1</v>
       </c>
       <c r="L33" s="80">
@@ -5879,7 +5879,7 @@
       <c r="H34" s="80"/>
       <c r="I34" s="79"/>
       <c r="J34" s="81"/>
-      <c r="K34" s="162"/>
+      <c r="K34" s="171"/>
       <c r="L34" s="80"/>
       <c r="M34" s="79"/>
       <c r="N34" s="81"/>
@@ -5939,7 +5939,7 @@
       <c r="J35" s="81">
         <v>0</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="172"/>
       <c r="L35" s="80">
         <v>0</v>
       </c>
@@ -6029,7 +6029,7 @@
       <c r="J36" s="81">
         <v>0</v>
       </c>
-      <c r="K36" s="161">
+      <c r="K36" s="170">
         <v>1</v>
       </c>
       <c r="L36" s="80">
@@ -6039,7 +6039,7 @@
       <c r="N36" s="81">
         <v>0</v>
       </c>
-      <c r="O36" s="167">
+      <c r="O36" s="173">
         <v>1</v>
       </c>
       <c r="P36" s="81">
@@ -6121,7 +6121,7 @@
       <c r="J37" s="81">
         <v>0</v>
       </c>
-      <c r="K37" s="162"/>
+      <c r="K37" s="171"/>
       <c r="L37" s="80">
         <v>0</v>
       </c>
@@ -6129,7 +6129,7 @@
       <c r="N37" s="81">
         <v>0</v>
       </c>
-      <c r="O37" s="168"/>
+      <c r="O37" s="174"/>
       <c r="P37" s="81">
         <v>0</v>
       </c>
@@ -6219,7 +6219,7 @@
       <c r="J38" s="81">
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="172"/>
       <c r="L38" s="80">
         <v>0</v>
       </c>
@@ -6227,7 +6227,7 @@
       <c r="N38" s="81">
         <v>0</v>
       </c>
-      <c r="O38" s="169"/>
+      <c r="O38" s="175"/>
       <c r="P38" s="81">
         <v>0</v>
       </c>
@@ -6548,7 +6548,7 @@
         <f>SUM(S42:S49)</f>
         <v>1</v>
       </c>
-      <c r="T41" s="174">
+      <c r="T41" s="161">
         <v>2</v>
       </c>
       <c r="U41" s="32">
@@ -6665,7 +6665,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="79"/>
-      <c r="T42" s="175"/>
+      <c r="T42" s="162"/>
       <c r="U42" s="79">
         <v>1</v>
       </c>
@@ -6765,7 +6765,7 @@
       <c r="S43" s="79">
         <v>1</v>
       </c>
-      <c r="T43" s="175"/>
+      <c r="T43" s="162"/>
       <c r="U43" s="79"/>
       <c r="V43" s="80">
         <v>0</v>
@@ -6847,7 +6847,7 @@
       <c r="Q44" s="84"/>
       <c r="R44" s="80"/>
       <c r="S44" s="79"/>
-      <c r="T44" s="175"/>
+      <c r="T44" s="162"/>
       <c r="U44" s="79"/>
       <c r="V44" s="80"/>
       <c r="W44" s="79"/>
@@ -6902,7 +6902,7 @@
       <c r="L45" s="80">
         <v>0</v>
       </c>
-      <c r="M45" s="166"/>
+      <c r="M45" s="165"/>
       <c r="N45" s="81">
         <v>0</v>
       </c>
@@ -6917,7 +6917,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="79"/>
-      <c r="T45" s="175"/>
+      <c r="T45" s="162"/>
       <c r="U45" s="79"/>
       <c r="V45" s="80">
         <v>0</v>
@@ -7005,7 +7005,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="79"/>
-      <c r="T46" s="175"/>
+      <c r="T46" s="162"/>
       <c r="U46" s="79"/>
       <c r="V46" s="80">
         <v>0</v>
@@ -7080,7 +7080,7 @@
       <c r="J47" s="81">
         <v>0</v>
       </c>
-      <c r="K47" s="161">
+      <c r="K47" s="170">
         <v>1</v>
       </c>
       <c r="L47" s="80">
@@ -7105,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="S47" s="79"/>
-      <c r="T47" s="175"/>
+      <c r="T47" s="162"/>
       <c r="U47" s="79"/>
       <c r="V47" s="80">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       <c r="J48" s="81">
         <v>0</v>
       </c>
-      <c r="K48" s="163"/>
+      <c r="K48" s="172"/>
       <c r="L48" s="80">
         <v>0</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="79"/>
-      <c r="T48" s="175"/>
+      <c r="T48" s="162"/>
       <c r="U48" s="79">
         <v>1</v>
       </c>
@@ -7283,7 +7283,7 @@
         <v>0</v>
       </c>
       <c r="S49" s="66"/>
-      <c r="T49" s="175"/>
+      <c r="T49" s="162"/>
       <c r="U49" s="66"/>
       <c r="V49" s="67">
         <v>0</v>
@@ -7391,7 +7391,7 @@
         <f>SUM(S51:S60)</f>
         <v>4</v>
       </c>
-      <c r="T50" s="176"/>
+      <c r="T50" s="163"/>
       <c r="U50" s="32">
         <f>SUM(U51:U60)</f>
         <v>0</v>
@@ -7498,7 +7498,7 @@
       <c r="J51" s="81">
         <v>0</v>
       </c>
-      <c r="K51" s="161">
+      <c r="K51" s="170">
         <v>1</v>
       </c>
       <c r="L51" s="80">
@@ -7510,7 +7510,7 @@
       <c r="N51" s="81">
         <v>0</v>
       </c>
-      <c r="O51" s="167">
+      <c r="O51" s="173">
         <v>1</v>
       </c>
       <c r="P51" s="81">
@@ -7592,15 +7592,15 @@
       <c r="J52" s="81">
         <v>0</v>
       </c>
-      <c r="K52" s="162"/>
+      <c r="K52" s="171"/>
       <c r="L52" s="80">
         <v>0</v>
       </c>
-      <c r="M52" s="165"/>
+      <c r="M52" s="192"/>
       <c r="N52" s="81">
         <v>0</v>
       </c>
-      <c r="O52" s="168"/>
+      <c r="O52" s="174"/>
       <c r="P52" s="81">
         <v>0</v>
       </c>
@@ -7686,15 +7686,15 @@
       <c r="J53" s="81">
         <v>0</v>
       </c>
-      <c r="K53" s="163"/>
+      <c r="K53" s="172"/>
       <c r="L53" s="80">
         <v>0</v>
       </c>
-      <c r="M53" s="166"/>
+      <c r="M53" s="165"/>
       <c r="N53" s="81">
         <v>0</v>
       </c>
-      <c r="O53" s="169"/>
+      <c r="O53" s="175"/>
       <c r="P53" s="81">
         <v>0</v>
       </c>
@@ -8002,7 +8002,7 @@
       <c r="J56" s="81">
         <v>0</v>
       </c>
-      <c r="K56" s="161">
+      <c r="K56" s="170">
         <v>1</v>
       </c>
       <c r="L56" s="80">
@@ -8094,7 +8094,7 @@
       <c r="J57" s="81">
         <v>0</v>
       </c>
-      <c r="K57" s="163"/>
+      <c r="K57" s="172"/>
       <c r="L57" s="80">
         <v>0</v>
       </c>
@@ -8280,7 +8280,7 @@
       <c r="J59" s="81">
         <v>0</v>
       </c>
-      <c r="K59" s="172">
+      <c r="K59" s="166">
         <v>1</v>
       </c>
       <c r="L59" s="80">
@@ -8376,7 +8376,7 @@
       <c r="J60" s="68">
         <v>0</v>
       </c>
-      <c r="K60" s="173"/>
+      <c r="K60" s="167"/>
       <c r="L60" s="67">
         <v>0</v>
       </c>
@@ -8451,7 +8451,7 @@
       <c r="D61" s="74"/>
       <c r="E61" s="30">
         <f>SUM(E62:E69)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="31">
         <v>1</v>
@@ -8496,7 +8496,7 @@
         <f>SUM(Q62:Q69)</f>
         <v>6</v>
       </c>
-      <c r="R61" s="174">
+      <c r="R61" s="161">
         <v>2</v>
       </c>
       <c r="S61" s="32">
@@ -8635,7 +8635,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="84"/>
-      <c r="R62" s="175"/>
+      <c r="R62" s="162"/>
       <c r="S62" s="79"/>
       <c r="T62" s="80">
         <v>0</v>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="D63" s="44"/>
       <c r="E63" s="78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="79">
         <v>0</v>
@@ -8745,7 +8745,7 @@
       <c r="Q63" s="84">
         <v>1</v>
       </c>
-      <c r="R63" s="175"/>
+      <c r="R63" s="162"/>
       <c r="S63" s="79">
         <v>1</v>
       </c>
@@ -8845,7 +8845,7 @@
       <c r="Q64" s="84">
         <v>1</v>
       </c>
-      <c r="R64" s="175"/>
+      <c r="R64" s="162"/>
       <c r="S64" s="79"/>
       <c r="T64" s="80">
         <v>0</v>
@@ -8951,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="Q65" s="84"/>
-      <c r="R65" s="175"/>
+      <c r="R65" s="162"/>
       <c r="S65" s="79"/>
       <c r="T65" s="80">
         <v>0</v>
@@ -9057,7 +9057,7 @@
       <c r="Q66" s="84">
         <v>2</v>
       </c>
-      <c r="R66" s="175"/>
+      <c r="R66" s="162"/>
       <c r="S66" s="79">
         <v>2</v>
       </c>
@@ -9150,7 +9150,7 @@
       <c r="J67" s="81">
         <v>0</v>
       </c>
-      <c r="K67" s="161">
+      <c r="K67" s="170">
         <v>1</v>
       </c>
       <c r="L67" s="80">
@@ -9169,7 +9169,7 @@
       <c r="Q67" s="84">
         <v>1</v>
       </c>
-      <c r="R67" s="175"/>
+      <c r="R67" s="162"/>
       <c r="S67" s="79">
         <v>1</v>
       </c>
@@ -9248,11 +9248,11 @@
       <c r="J68" s="81">
         <v>0</v>
       </c>
-      <c r="K68" s="163"/>
+      <c r="K68" s="172"/>
       <c r="L68" s="80">
         <v>0</v>
       </c>
-      <c r="M68" s="166"/>
+      <c r="M68" s="165"/>
       <c r="N68" s="81">
         <v>0</v>
       </c>
@@ -9265,7 +9265,7 @@
       <c r="Q68" s="84">
         <v>1</v>
       </c>
-      <c r="R68" s="175"/>
+      <c r="R68" s="162"/>
       <c r="S68" s="79"/>
       <c r="T68" s="80">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>0</v>
       </c>
       <c r="Q69" s="70"/>
-      <c r="R69" s="175"/>
+      <c r="R69" s="162"/>
       <c r="S69" s="66"/>
       <c r="T69" s="67">
         <v>0</v>
@@ -9464,7 +9464,7 @@
         <f>SUM(Q71:Q78)</f>
         <v>1</v>
       </c>
-      <c r="R70" s="176"/>
+      <c r="R70" s="163"/>
       <c r="S70" s="32">
         <f>SUM(S71:S78)</f>
         <v>2</v>
@@ -9583,7 +9583,7 @@
       <c r="J71" s="81">
         <v>0</v>
       </c>
-      <c r="K71" s="161">
+      <c r="K71" s="170">
         <v>1</v>
       </c>
       <c r="L71" s="80">
@@ -9677,7 +9677,7 @@
       <c r="J72" s="81">
         <v>0</v>
       </c>
-      <c r="K72" s="162"/>
+      <c r="K72" s="171"/>
       <c r="L72" s="80">
         <v>0</v>
       </c>
@@ -9767,7 +9767,7 @@
       <c r="J73" s="81">
         <v>0</v>
       </c>
-      <c r="K73" s="163"/>
+      <c r="K73" s="172"/>
       <c r="L73" s="80">
         <v>0</v>
       </c>
@@ -9871,7 +9871,7 @@
       <c r="N74" s="81">
         <v>0</v>
       </c>
-      <c r="O74" s="167">
+      <c r="O74" s="173">
         <v>1</v>
       </c>
       <c r="P74" s="81">
@@ -9971,7 +9971,7 @@
       <c r="N75" s="81">
         <v>0</v>
       </c>
-      <c r="O75" s="169"/>
+      <c r="O75" s="175"/>
       <c r="P75" s="81">
         <v>0</v>
       </c>
@@ -10053,7 +10053,7 @@
       <c r="J76" s="81">
         <v>0</v>
       </c>
-      <c r="K76" s="161">
+      <c r="K76" s="170">
         <v>1</v>
       </c>
       <c r="L76" s="80">
@@ -10147,7 +10147,7 @@
       <c r="J77" s="81">
         <v>0</v>
       </c>
-      <c r="K77" s="163"/>
+      <c r="K77" s="172"/>
       <c r="L77" s="80">
         <v>0</v>
       </c>
@@ -11019,7 +11019,7 @@
       <c r="J85" s="112">
         <v>0</v>
       </c>
-      <c r="K85" s="181">
+      <c r="K85" s="189">
         <v>1</v>
       </c>
       <c r="L85" s="79">
@@ -11129,11 +11129,11 @@
       <c r="J86" s="127">
         <v>0</v>
       </c>
-      <c r="K86" s="182"/>
+      <c r="K86" s="190"/>
       <c r="L86" s="91">
         <v>0</v>
       </c>
-      <c r="M86" s="183"/>
+      <c r="M86" s="191"/>
       <c r="N86" s="127">
         <v>0</v>
       </c>
@@ -11363,86 +11363,86 @@
       <c r="B89" s="140"/>
       <c r="C89" s="140"/>
       <c r="D89" s="140"/>
-      <c r="E89" s="177" t="s">
+      <c r="E89" s="185" t="s">
         <v>114</v>
       </c>
-      <c r="F89" s="171"/>
-      <c r="G89" s="177" t="s">
+      <c r="F89" s="186"/>
+      <c r="G89" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="H89" s="171"/>
-      <c r="I89" s="177" t="s">
+      <c r="H89" s="186"/>
+      <c r="I89" s="185" t="s">
         <v>116</v>
       </c>
-      <c r="J89" s="171"/>
-      <c r="K89" s="177" t="s">
+      <c r="J89" s="186"/>
+      <c r="K89" s="185" t="s">
         <v>117</v>
       </c>
-      <c r="L89" s="171"/>
-      <c r="M89" s="178" t="s">
+      <c r="L89" s="186"/>
+      <c r="M89" s="188" t="s">
         <v>118</v>
       </c>
-      <c r="N89" s="171"/>
-      <c r="O89" s="178" t="s">
+      <c r="N89" s="186"/>
+      <c r="O89" s="188" t="s">
         <v>119</v>
       </c>
-      <c r="P89" s="171"/>
-      <c r="Q89" s="170" t="s">
+      <c r="P89" s="186"/>
+      <c r="Q89" s="187" t="s">
         <v>120</v>
       </c>
-      <c r="R89" s="171"/>
-      <c r="S89" s="170" t="s">
+      <c r="R89" s="186"/>
+      <c r="S89" s="187" t="s">
         <v>121</v>
       </c>
-      <c r="T89" s="171"/>
-      <c r="U89" s="170" t="s">
+      <c r="T89" s="186"/>
+      <c r="U89" s="187" t="s">
         <v>122</v>
       </c>
-      <c r="V89" s="171"/>
-      <c r="W89" s="170" t="s">
+      <c r="V89" s="186"/>
+      <c r="W89" s="187" t="s">
         <v>123</v>
       </c>
-      <c r="X89" s="171"/>
-      <c r="Y89" s="170" t="s">
+      <c r="X89" s="186"/>
+      <c r="Y89" s="187" t="s">
         <v>124</v>
       </c>
-      <c r="Z89" s="171"/>
-      <c r="AA89" s="170" t="s">
+      <c r="Z89" s="186"/>
+      <c r="AA89" s="187" t="s">
         <v>122</v>
       </c>
-      <c r="AB89" s="171"/>
-      <c r="AC89" s="178" t="s">
+      <c r="AB89" s="186"/>
+      <c r="AC89" s="188" t="s">
         <v>125</v>
       </c>
-      <c r="AD89" s="171"/>
-      <c r="AE89" s="178" t="s">
+      <c r="AD89" s="186"/>
+      <c r="AE89" s="188" t="s">
         <v>126</v>
       </c>
-      <c r="AF89" s="171"/>
-      <c r="AG89" s="178" t="s">
+      <c r="AF89" s="186"/>
+      <c r="AG89" s="188" t="s">
         <v>127</v>
       </c>
-      <c r="AH89" s="171"/>
-      <c r="AI89" s="178" t="s">
+      <c r="AH89" s="186"/>
+      <c r="AI89" s="188" t="s">
         <v>127</v>
       </c>
-      <c r="AJ89" s="171"/>
-      <c r="AK89" s="178" t="s">
+      <c r="AJ89" s="186"/>
+      <c r="AK89" s="188" t="s">
         <v>128</v>
       </c>
-      <c r="AL89" s="171"/>
-      <c r="AM89" s="177" t="s">
+      <c r="AL89" s="186"/>
+      <c r="AM89" s="185" t="s">
         <v>129</v>
       </c>
-      <c r="AN89" s="171"/>
-      <c r="AO89" s="177" t="s">
+      <c r="AN89" s="186"/>
+      <c r="AO89" s="185" t="s">
         <v>130</v>
       </c>
-      <c r="AP89" s="171"/>
-      <c r="AQ89" s="177" t="s">
+      <c r="AP89" s="186"/>
+      <c r="AQ89" s="185" t="s">
         <v>131</v>
       </c>
-      <c r="AR89" s="171"/>
+      <c r="AR89" s="186"/>
       <c r="AS89" s="141"/>
     </row>
     <row r="90" spans="1:45" ht="12.75" customHeight="1">
@@ -54351,23 +54351,51 @@
   </sheetData>
   <autoFilter ref="E6:AR87" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="78">
-    <mergeCell ref="T41:T50"/>
-    <mergeCell ref="M44:M45"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="K33:K35"/>
-    <mergeCell ref="K36:K38"/>
-    <mergeCell ref="O36:O38"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="M28:M29"/>
-    <mergeCell ref="O28:O29"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="K51:K53"/>
+    <mergeCell ref="M51:M53"/>
+    <mergeCell ref="O51:O53"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="Y89:Z89"/>
+    <mergeCell ref="K59:K60"/>
+    <mergeCell ref="R61:R70"/>
+    <mergeCell ref="K67:K68"/>
+    <mergeCell ref="M67:M68"/>
+    <mergeCell ref="K71:K73"/>
+    <mergeCell ref="AQ89:AR89"/>
+    <mergeCell ref="AA89:AB89"/>
+    <mergeCell ref="AC89:AD89"/>
+    <mergeCell ref="AE89:AF89"/>
+    <mergeCell ref="AG89:AH89"/>
+    <mergeCell ref="AI89:AJ89"/>
+    <mergeCell ref="AK89:AL89"/>
+    <mergeCell ref="AM89:AN89"/>
+    <mergeCell ref="AO89:AP89"/>
+    <mergeCell ref="AI5:AJ5"/>
+    <mergeCell ref="AK5:AL5"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="Q89:R89"/>
+    <mergeCell ref="S89:T89"/>
+    <mergeCell ref="O89:P89"/>
+    <mergeCell ref="O74:O75"/>
+    <mergeCell ref="K76:K77"/>
+    <mergeCell ref="K85:K86"/>
+    <mergeCell ref="M85:M86"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="U89:V89"/>
+    <mergeCell ref="W89:X89"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AC5:AD5"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="AG5:AH5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
     <mergeCell ref="AM7:AR7"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="C5:C6"/>
@@ -54384,51 +54412,23 @@
     <mergeCell ref="AM5:AN5"/>
     <mergeCell ref="AO5:AP5"/>
     <mergeCell ref="AQ5:AR5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="AC5:AD5"/>
-    <mergeCell ref="AE5:AF5"/>
-    <mergeCell ref="AG5:AH5"/>
-    <mergeCell ref="AI5:AJ5"/>
-    <mergeCell ref="AK5:AL5"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="Q89:R89"/>
-    <mergeCell ref="S89:T89"/>
-    <mergeCell ref="O89:P89"/>
-    <mergeCell ref="O74:O75"/>
-    <mergeCell ref="K76:K77"/>
-    <mergeCell ref="K85:K86"/>
-    <mergeCell ref="M85:M86"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="M89:N89"/>
-    <mergeCell ref="U89:V89"/>
-    <mergeCell ref="W89:X89"/>
-    <mergeCell ref="AQ89:AR89"/>
-    <mergeCell ref="AA89:AB89"/>
-    <mergeCell ref="AC89:AD89"/>
-    <mergeCell ref="AE89:AF89"/>
-    <mergeCell ref="AG89:AH89"/>
-    <mergeCell ref="AI89:AJ89"/>
-    <mergeCell ref="AK89:AL89"/>
-    <mergeCell ref="AM89:AN89"/>
-    <mergeCell ref="AO89:AP89"/>
-    <mergeCell ref="K51:K53"/>
-    <mergeCell ref="M51:M53"/>
-    <mergeCell ref="O51:O53"/>
-    <mergeCell ref="K56:K57"/>
-    <mergeCell ref="Y89:Z89"/>
-    <mergeCell ref="K59:K60"/>
-    <mergeCell ref="R61:R70"/>
-    <mergeCell ref="K67:K68"/>
-    <mergeCell ref="M67:M68"/>
-    <mergeCell ref="K71:K73"/>
+    <mergeCell ref="M28:M29"/>
+    <mergeCell ref="O28:O29"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="T41:T50"/>
+    <mergeCell ref="M44:M45"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="K33:K35"/>
+    <mergeCell ref="K36:K38"/>
+    <mergeCell ref="O36:O38"/>
+    <mergeCell ref="K47:K48"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:AR8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
@@ -54459,7 +54459,7 @@
       <c r="C1" s="151"/>
     </row>
     <row r="2" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A2" s="193" t="s">
+      <c r="A2" s="195" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="152" t="s">
@@ -54509,7 +54509,7 @@
       <c r="AP2" s="154"/>
     </row>
     <row r="3" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A3" s="187"/>
+      <c r="A3" s="182"/>
       <c r="B3" s="156" t="s">
         <v>25</v>
       </c>
@@ -54521,7 +54521,7 @@
       </c>
     </row>
     <row r="4" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A4" s="193" t="s">
+      <c r="A4" s="195" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="156" t="s">
@@ -54532,7 +54532,7 @@
       </c>
     </row>
     <row r="5" spans="1:42" ht="14.4">
-      <c r="A5" s="187"/>
+      <c r="A5" s="182"/>
       <c r="B5" s="156" t="s">
         <v>25</v>
       </c>
@@ -54544,7 +54544,7 @@
       </c>
     </row>
     <row r="6" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A6" s="193" t="s">
+      <c r="A6" s="195" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="156" t="s">
@@ -54555,20 +54555,20 @@
       </c>
     </row>
     <row r="7" spans="1:42" ht="14.4">
-      <c r="A7" s="187"/>
+      <c r="A7" s="182"/>
       <c r="B7" s="156" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="153">
         <v>8</v>
       </c>
-      <c r="D7" s="194" t="s">
+      <c r="D7" s="200" t="s">
         <v>116</v>
       </c>
-      <c r="E7" s="195"/>
+      <c r="E7" s="201"/>
     </row>
     <row r="8" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A8" s="193" t="s">
+      <c r="A8" s="195" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="156" t="s">
@@ -54579,7 +54579,7 @@
       </c>
     </row>
     <row r="9" spans="1:42" ht="14.4">
-      <c r="A9" s="187"/>
+      <c r="A9" s="182"/>
       <c r="B9" s="156" t="s">
         <v>25</v>
       </c>
@@ -54591,7 +54591,7 @@
       </c>
     </row>
     <row r="10" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A10" s="193" t="s">
+      <c r="A10" s="195" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="156" t="s">
@@ -54602,7 +54602,7 @@
       </c>
     </row>
     <row r="11" spans="1:42" ht="14.4">
-      <c r="A11" s="187"/>
+      <c r="A11" s="182"/>
       <c r="B11" s="156" t="s">
         <v>25</v>
       </c>
@@ -54614,7 +54614,7 @@
       </c>
     </row>
     <row r="12" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A12" s="193" t="s">
+      <c r="A12" s="195" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="156" t="s">
@@ -54625,7 +54625,7 @@
       </c>
     </row>
     <row r="13" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A13" s="187"/>
+      <c r="A13" s="182"/>
       <c r="B13" s="156" t="s">
         <v>25</v>
       </c>
@@ -54637,7 +54637,7 @@
       </c>
     </row>
     <row r="14" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A14" s="193" t="s">
+      <c r="A14" s="195" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="156" t="s">
@@ -54648,7 +54648,7 @@
       </c>
     </row>
     <row r="15" spans="1:42" ht="14.4">
-      <c r="A15" s="187"/>
+      <c r="A15" s="182"/>
       <c r="B15" s="156" t="s">
         <v>25</v>
       </c>
@@ -54660,7 +54660,7 @@
       </c>
     </row>
     <row r="16" spans="1:42" ht="22.5" customHeight="1">
-      <c r="A16" s="193" t="s">
+      <c r="A16" s="195" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="156" t="s">
@@ -54671,7 +54671,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A17" s="187"/>
+      <c r="A17" s="182"/>
       <c r="B17" s="156" t="s">
         <v>25</v>
       </c>
@@ -54680,7 +54680,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A18" s="193" t="s">
+      <c r="A18" s="195" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="156" t="s">
@@ -54691,7 +54691,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A19" s="187"/>
+      <c r="A19" s="182"/>
       <c r="B19" s="156" t="s">
         <v>25</v>
       </c>
@@ -54700,7 +54700,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A20" s="193" t="s">
+      <c r="A20" s="195" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="156" t="s">
@@ -54711,7 +54711,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A21" s="187"/>
+      <c r="A21" s="182"/>
       <c r="B21" s="156" t="s">
         <v>25</v>
       </c>
@@ -54720,7 +54720,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A22" s="193" t="s">
+      <c r="A22" s="195" t="s">
         <v>14</v>
       </c>
       <c r="B22" s="156" t="s">
@@ -54731,7 +54731,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A23" s="187"/>
+      <c r="A23" s="182"/>
       <c r="B23" s="156" t="s">
         <v>25</v>
       </c>
@@ -54740,7 +54740,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A24" s="193" t="s">
+      <c r="A24" s="195" t="s">
         <v>15</v>
       </c>
       <c r="B24" s="156" t="s">
@@ -54751,7 +54751,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A25" s="187"/>
+      <c r="A25" s="182"/>
       <c r="B25" s="156" t="s">
         <v>25</v>
       </c>
@@ -54760,7 +54760,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A26" s="193" t="s">
+      <c r="A26" s="195" t="s">
         <v>16</v>
       </c>
       <c r="B26" s="156" t="s">
@@ -54771,7 +54771,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A27" s="187"/>
+      <c r="A27" s="182"/>
       <c r="B27" s="156" t="s">
         <v>25</v>
       </c>
@@ -54780,7 +54780,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A28" s="193" t="s">
+      <c r="A28" s="195" t="s">
         <v>17</v>
       </c>
       <c r="B28" s="156" t="s">
@@ -54791,7 +54791,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A29" s="187"/>
+      <c r="A29" s="182"/>
       <c r="B29" s="156" t="s">
         <v>25</v>
       </c>
@@ -54800,7 +54800,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A30" s="193" t="s">
+      <c r="A30" s="195" t="s">
         <v>18</v>
       </c>
       <c r="B30" s="156" t="s">
@@ -54811,7 +54811,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A31" s="187"/>
+      <c r="A31" s="182"/>
       <c r="B31" s="156" t="s">
         <v>25</v>
       </c>
@@ -54820,7 +54820,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A32" s="193" t="s">
+      <c r="A32" s="195" t="s">
         <v>19</v>
       </c>
       <c r="B32" s="156" t="s">
@@ -54831,7 +54831,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="22.5" customHeight="1">
-      <c r="A33" s="187"/>
+      <c r="A33" s="182"/>
       <c r="B33" s="156" t="s">
         <v>25</v>
       </c>
@@ -54840,7 +54840,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="22.5" customHeight="1">
-      <c r="A34" s="193" t="s">
+      <c r="A34" s="195" t="s">
         <v>20</v>
       </c>
       <c r="B34" s="156" t="s">
@@ -54851,7 +54851,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="22.5" customHeight="1">
-      <c r="A35" s="187"/>
+      <c r="A35" s="182"/>
       <c r="B35" s="156" t="s">
         <v>25</v>
       </c>
@@ -54860,7 +54860,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="22.5" customHeight="1">
-      <c r="A36" s="198" t="s">
+      <c r="A36" s="196" t="s">
         <v>21</v>
       </c>
       <c r="B36" s="152" t="s">
@@ -54871,20 +54871,20 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="14.4">
-      <c r="A37" s="199"/>
+      <c r="A37" s="197"/>
       <c r="B37" s="156" t="s">
         <v>25</v>
       </c>
       <c r="C37" s="153">
         <v>8</v>
       </c>
-      <c r="D37" s="200" t="s">
+      <c r="D37" s="198" t="s">
         <v>129</v>
       </c>
-      <c r="E37" s="201"/>
+      <c r="E37" s="199"/>
     </row>
     <row r="38" spans="1:5" ht="22.5" customHeight="1">
-      <c r="A38" s="193" t="s">
+      <c r="A38" s="195" t="s">
         <v>22</v>
       </c>
       <c r="B38" s="156" t="s">
@@ -54895,7 +54895,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="14.4">
-      <c r="A39" s="187"/>
+      <c r="A39" s="182"/>
       <c r="B39" s="156" t="s">
         <v>25</v>
       </c>
@@ -54907,7 +54907,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="22.5" customHeight="1">
-      <c r="A40" s="193" t="s">
+      <c r="A40" s="195" t="s">
         <v>23</v>
       </c>
       <c r="B40" s="156" t="s">
@@ -54918,17 +54918,17 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="14.4">
-      <c r="A41" s="187"/>
+      <c r="A41" s="182"/>
       <c r="B41" s="156" t="s">
         <v>25</v>
       </c>
       <c r="C41" s="153">
         <v>8</v>
       </c>
-      <c r="D41" s="196" t="s">
+      <c r="D41" s="193" t="s">
         <v>131</v>
       </c>
-      <c r="E41" s="197"/>
+      <c r="E41" s="194"/>
     </row>
     <row r="42" spans="1:5" ht="14.4">
       <c r="C42" s="151"/>
@@ -57809,6 +57809,21 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A40:A41"/>
     <mergeCell ref="D41:E41"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A30:A31"/>
@@ -57817,21 +57832,6 @@
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="D37:E37"/>
     <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A8:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
